--- a/ExcelOutputs/frequency.xlsx
+++ b/ExcelOutputs/frequency.xlsx
@@ -9,6 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calculator" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modified Calculator" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="no turns" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 turns" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="Deck">Calculator!$B$4</definedName>
@@ -3286,105 +3287,594 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="22" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Normal Unit</t>
         </is>
       </c>
-      <c r="C1" s="22" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Target Unit</t>
         </is>
       </c>
-      <c r="D1" s="22" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="E1" s="22" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="F1" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G1" s="22" t="n">
+      <c r="F1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1" t="n">
         <v>1</v>
       </c>
-      <c r="H1" s="22" t="n">
+      <c r="H1" t="n">
         <v>2</v>
       </c>
-      <c r="I1" s="22" t="n">
+      <c r="I1" t="n">
         <v>3</v>
       </c>
-      <c r="J1" s="22" t="n">
+      <c r="J1" t="n">
         <v>4</v>
       </c>
-      <c r="K1" s="22" t="n">
+      <c r="K1" t="n">
         <v>5</v>
       </c>
-      <c r="L1" s="22" t="n">
+      <c r="L1" t="n">
         <v>6</v>
       </c>
-      <c r="M1" s="22" t="n">
+      <c r="M1" t="n">
         <v>7</v>
       </c>
-      <c r="N1" s="22" t="n">
+      <c r="N1" t="n">
         <v>8</v>
       </c>
-      <c r="O1" s="22" t="n">
+      <c r="O1" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4437</v>
+        <v>0.519</v>
       </c>
       <c r="E2" t="n">
         <v>1000000</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5516</v>
+        <v>0.4699</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3704</v>
+        <v>0.4088</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0733</v>
+        <v>0.1102</v>
       </c>
       <c r="I2" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>30</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4435</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5518</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0728</v>
+      </c>
+      <c r="I3" t="n">
         <v>0.0046</v>
       </c>
+      <c r="J3" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>31</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.6442</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0398</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>32</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2509</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7491</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.2365</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0144</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>33</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Normal Unit</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Target Unit</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="F1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1" t="n">
+        <v>5</v>
+      </c>
+      <c r="L1" t="n">
+        <v>6</v>
+      </c>
+      <c r="M1" t="n">
+        <v>7</v>
+      </c>
+      <c r="N1" t="n">
+        <v>8</v>
+      </c>
+      <c r="O1" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.8099</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8099</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1901</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
       <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6523</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0327</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>31</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.6099</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5219</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3901</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>30</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.5707</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4123</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4293</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.1406</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.0005999999999999999</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>29</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.5633</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4367</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1969</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="K6" t="n">
         <v>0.0001</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
         <v>0</v>
       </c>
     </row>
